--- a/Foundation of Data Analysis/Data-Exploration-Excel/Analysing-Data/Excel-Calculation-Functions/Excel-Calculation-function.xlsx
+++ b/Foundation of Data Analysis/Data-Exploration-Excel/Analysing-Data/Excel-Calculation-Functions/Excel-Calculation-function.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DS-ML-COURSE\Foundation of Data Analysis\Data-Exploration-Excel\Analysing-Data\Excel-Calculation-Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9738C42C-E980-4249-822A-CA9A525D5651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAB160BC-59A3-43FD-A2E0-80951455DD9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7CB6D2A0-124E-4403-AC55-312AF559C2D9}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="19420" windowHeight="10300" xr2:uid="{7CB6D2A0-124E-4403-AC55-312AF559C2D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,10 +24,74 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Salary</t>
+  </si>
+  <si>
+    <t>Amit Sharma</t>
+  </si>
+  <si>
+    <t>Neha Verma</t>
+  </si>
+  <si>
+    <t>Rahul Singh</t>
+  </si>
+  <si>
+    <t>Priya Gupta</t>
+  </si>
+  <si>
+    <t>Ankit Kumar</t>
+  </si>
+  <si>
+    <t>Rohit Mehta</t>
+  </si>
+  <si>
+    <t>Pooja Yadav</t>
+  </si>
+  <si>
+    <t>Karan Malhotra</t>
+  </si>
+  <si>
+    <t>Sneha Kapoor</t>
+  </si>
+  <si>
+    <t>Vikram Joshi</t>
+  </si>
+  <si>
+    <t>MIN</t>
+  </si>
+  <si>
+    <t>MAX</t>
+  </si>
+  <si>
+    <t>SUM</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>median</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -55,8 +119,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -371,9 +441,137 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8831B656-DC9C-42D8-90D9-3BEA151956BB}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="20.36328125" customWidth="1"/>
+    <col min="2" max="2" width="14.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2">
+        <v>52000</v>
+      </c>
+      <c r="D2">
+        <f>MIN(B2:B11)</f>
+        <v>46000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2">
+        <v>52000</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2">
+        <v>48000</v>
+      </c>
+      <c r="D4">
+        <f>MAX(B2:B11)</f>
+        <v>56000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2">
+        <v>55000</v>
+      </c>
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="2">
+        <v>55000</v>
+      </c>
+      <c r="D6">
+        <f>SUM(B2:B11)</f>
+        <v>522000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="2">
+        <v>52000</v>
+      </c>
+      <c r="D7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="2">
+        <v>46000</v>
+      </c>
+      <c r="D8">
+        <f>AVERAGE(B2:B11)</f>
+        <v>52200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="2">
+        <v>53000</v>
+      </c>
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="2">
+        <v>53000</v>
+      </c>
+      <c r="D10">
+        <f>MEDIAN(B2:B11)</f>
+        <v>52500</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="2">
+        <v>56000</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>